--- a/dataset/large/Map_Data_Large_with_Geofencing.xlsx
+++ b/dataset/large/Map_Data_Large_with_Geofencing.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74f3fc933c58b622/Desktop/UATM/dataset/large/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_FFC65FC04451ACF926170BB72370E1587F483327" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5807D02-7DA5-4EB8-9A60-DDABEFD28CC6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -163,8 +169,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,13 +233,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -271,7 +285,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -305,6 +319,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -339,9 +354,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -514,11 +530,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="21.21875" customWidth="1"/>
+    <col min="3" max="3" width="121.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,7 +549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>13</v>
       </c>
@@ -537,7 +557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -548,7 +568,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -556,12 +576,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -569,17 +589,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -590,12 +610,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -606,7 +626,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -614,7 +634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -625,7 +645,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -636,7 +656,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -647,7 +667,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -658,7 +678,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -669,7 +689,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -677,7 +697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -688,12 +708,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -701,12 +721,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -714,7 +734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -725,7 +745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -736,7 +756,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>13</v>
       </c>
@@ -744,7 +764,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -755,7 +775,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>16</v>
       </c>
@@ -763,7 +783,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -774,7 +794,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -785,12 +805,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -801,7 +821,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -812,7 +832,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>15</v>
       </c>
@@ -820,7 +840,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -831,17 +851,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>15</v>
       </c>
@@ -849,7 +869,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>16</v>
       </c>
@@ -857,7 +877,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>18</v>
       </c>
@@ -865,12 +885,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -881,12 +901,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -897,12 +917,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -913,7 +933,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -924,12 +944,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -940,7 +960,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -951,7 +971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>16</v>
       </c>
@@ -959,7 +979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>16</v>
       </c>
@@ -967,17 +987,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>13</v>
       </c>
@@ -985,7 +1005,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -996,7 +1016,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -1007,7 +1027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1018,12 +1038,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1034,17 +1054,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -1055,12 +1075,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1071,7 +1091,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -1082,12 +1102,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -1098,7 +1118,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -1109,7 +1129,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -1120,7 +1140,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>16</v>
       </c>
@@ -1128,7 +1148,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -1139,7 +1159,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>13</v>
       </c>
@@ -1147,7 +1167,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -1158,17 +1178,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -1179,7 +1199,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -1190,7 +1210,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -1201,7 +1221,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -1212,7 +1232,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -1223,7 +1243,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -1234,7 +1254,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -1245,7 +1265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>16</v>
       </c>
@@ -1253,7 +1273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -1264,17 +1284,17 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>18</v>
       </c>
@@ -1282,7 +1302,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>27</v>
       </c>
@@ -1290,7 +1310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>13</v>
       </c>
@@ -1298,12 +1318,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -1314,12 +1334,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>18</v>
       </c>
@@ -1327,7 +1347,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>27</v>
       </c>
@@ -1335,7 +1355,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1363,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C97" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>16</v>
       </c>
@@ -1356,12 +1376,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C99" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>18</v>
       </c>
@@ -1369,12 +1389,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C101" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -1385,7 +1405,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -1396,7 +1416,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -1407,7 +1427,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>18</v>
       </c>
@@ -1415,7 +1435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>15</v>
       </c>
@@ -1423,7 +1443,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -1434,7 +1454,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -1445,12 +1465,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C109" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -1472,7 +1492,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -1483,12 +1503,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -1499,7 +1519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -1510,7 +1530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>16</v>
       </c>
@@ -1518,7 +1538,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>3</v>
       </c>
@@ -1529,17 +1549,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C118" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>15</v>
       </c>
@@ -1547,7 +1567,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -1558,7 +1578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>18</v>
       </c>
@@ -1566,12 +1586,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -1582,7 +1602,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>18</v>
       </c>
@@ -1590,7 +1610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>3</v>
       </c>
@@ -1609,7 +1629,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1640,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -1631,17 +1651,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C130" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C131" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>3</v>
       </c>
@@ -1652,7 +1672,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>15</v>
       </c>
@@ -1660,7 +1680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>12</v>
       </c>
@@ -1671,7 +1691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>13</v>
       </c>
@@ -1679,22 +1699,22 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C138" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>27</v>
       </c>
@@ -1702,7 +1722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -1713,7 +1733,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>18</v>
       </c>
@@ -1721,7 +1741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -1732,7 +1752,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -1743,7 +1763,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -1754,7 +1774,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>18</v>
       </c>
@@ -1762,7 +1782,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>13</v>
       </c>
@@ -1770,7 +1790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>3</v>
       </c>
@@ -1781,7 +1801,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>27</v>
       </c>
@@ -1789,12 +1809,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C149" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>12</v>
       </c>
@@ -1805,22 +1825,22 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C152" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C153" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -1831,7 +1851,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>13</v>
       </c>
@@ -1839,7 +1859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -1850,7 +1870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>13</v>
       </c>
@@ -1858,7 +1878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -1869,12 +1889,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>27</v>
       </c>
@@ -1882,7 +1902,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>18</v>
       </c>
@@ -1890,7 +1910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -1901,17 +1921,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -1922,12 +1942,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>3</v>
       </c>
@@ -1938,7 +1958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -1949,12 +1969,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -1965,7 +1985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -1976,12 +1996,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>12</v>
       </c>
@@ -1992,7 +2012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -2003,7 +2023,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -2014,7 +2034,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>12</v>
       </c>
@@ -2025,12 +2045,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C177" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -2041,7 +2061,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -2052,7 +2072,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -2063,7 +2083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>27</v>
       </c>
@@ -2071,7 +2091,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>18</v>
       </c>
@@ -2079,7 +2099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>13</v>
       </c>
@@ -2087,12 +2107,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C184" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>8</v>
       </c>
@@ -2103,12 +2123,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C186" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -2119,17 +2139,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C188" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -2140,7 +2160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -2151,7 +2171,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>27</v>
       </c>
@@ -2159,7 +2179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>15</v>
       </c>
@@ -2167,12 +2187,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C194" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>16</v>
       </c>
@@ -2180,7 +2200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -2191,7 +2211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -2202,7 +2222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -2213,7 +2233,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>7</v>
       </c>
@@ -2224,12 +2244,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>4</v>
       </c>
